--- a/students.xlsx
+++ b/students.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ИС-21" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ИС-22" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ИС-23" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПИ-22" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="АРХ-20" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,14 +438,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Пётр</t>
+          <t>Иван</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Сидорова</t>
+          <t>Петрова</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -457,12 +457,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Кузнецов</t>
+          <t>Козлов</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Дмитрий</t>
         </is>
       </c>
     </row>
@@ -495,24 +495,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Петров</t>
+          <t>Сидоров</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Олег</t>
+          <t>Семён</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Смирнова</t>
+          <t>Орлова</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Елена</t>
+          <t>Мария</t>
         </is>
       </c>
     </row>
